--- a/artfynd/A 41276-2025 artfynd.xlsx
+++ b/artfynd/A 41276-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3929922</v>
+        <v>3477775</v>
       </c>
       <c r="B2" t="n">
-        <v>99397</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>220785</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690934.6695978683</v>
+        <v>690935</v>
       </c>
       <c r="R2" t="n">
-        <v>6629255.505416888</v>
+        <v>6629256</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>2009-09-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2009-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3477775</v>
+        <v>3929922</v>
       </c>
       <c r="B3" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>690934.6695978683</v>
+        <v>690935</v>
       </c>
       <c r="R3" t="n">
-        <v>6629255.505416888</v>
+        <v>6629256</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +845,9 @@
           <t>2009-09-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2009-09-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,12 +882,7 @@
         <v>4239052</v>
       </c>
       <c r="B4" t="n">
-        <v>101119</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>690934.6695978683</v>
+        <v>690935</v>
       </c>
       <c r="R4" t="n">
-        <v>6629255.505416888</v>
+        <v>6629256</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,19 +947,9 @@
           <t>2009-09-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2009-09-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5050744</v>
+        <v>5050743</v>
       </c>
       <c r="B5" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1062,14 +1012,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Värnbacken i N delen, Upl</t>
+          <t>Värnbacken, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690937.0403480352</v>
+        <v>690935</v>
       </c>
       <c r="R5" t="n">
-        <v>6629337.396477405</v>
+        <v>6629256</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,19 +1049,9 @@
           <t>2009-09-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2009-09-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5050745</v>
+        <v>5050744</v>
       </c>
       <c r="B6" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,14 +1114,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Värnbacken, 200 m O om, Upl</t>
+          <t>Värnbacken i N delen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691028.8213170489</v>
+        <v>690937</v>
       </c>
       <c r="R6" t="n">
-        <v>6629420.846782985</v>
+        <v>6629337</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1216,21 +1151,11 @@
           <t>2009-09-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2009-09-23</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1242,7 +1167,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>betad hassellund</t>
+          <t>blockig lövskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1260,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5050743</v>
+        <v>5050745</v>
       </c>
       <c r="B7" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,14 +1216,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Värnbacken, Upl</t>
+          <t>Värnbacken, 200 m O om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>690934.6695978683</v>
+        <v>691029</v>
       </c>
       <c r="R7" t="n">
-        <v>6629255.505416888</v>
+        <v>6629421</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1333,21 +1253,11 @@
           <t>2009-09-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2009-09-23</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1359,7 +1269,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>blockig lövskog</t>
+          <t>betad hassellund</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 41276-2025 artfynd.xlsx
+++ b/artfynd/A 41276-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3477775</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3929922</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4239052</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5050743</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5050744</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,8 +1314,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5050745</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>